--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/111.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/111.xlsx
@@ -426,13 +426,13 @@
         <v>-15.56820883095602</v>
       </c>
       <c r="E2">
-        <v>-14.11456270209293</v>
+        <v>-15.71103998570505</v>
       </c>
       <c r="F2">
-        <v>-3.517843735696821</v>
+        <v>-4.3335387739683</v>
       </c>
       <c r="G2">
-        <v>-10.33475958825341</v>
+        <v>-10.11676347503794</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.5040234533136</v>
       </c>
       <c r="E3">
-        <v>-14.5252183105305</v>
+        <v>-16.35471728115532</v>
       </c>
       <c r="F3">
-        <v>-3.353690309321057</v>
+        <v>-4.552881350188178</v>
       </c>
       <c r="G3">
-        <v>-10.71988859301898</v>
+        <v>-10.82763029759456</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.53166372503447</v>
       </c>
       <c r="E4">
-        <v>-14.68364697368885</v>
+        <v>-15.6735170500775</v>
       </c>
       <c r="F4">
-        <v>-3.232838960559235</v>
+        <v>-4.078031333677001</v>
       </c>
       <c r="G4">
-        <v>-9.64444463240458</v>
+        <v>-10.84549731187001</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.63028413007339</v>
       </c>
       <c r="E5">
-        <v>-15.63926820115749</v>
+        <v>-16.97552578286685</v>
       </c>
       <c r="F5">
-        <v>-3.480020480084996</v>
+        <v>-4.09811675809268</v>
       </c>
       <c r="G5">
-        <v>-9.061583363669417</v>
+        <v>-10.18477863314227</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.7497825589946</v>
       </c>
       <c r="E6">
-        <v>-16.90717299619507</v>
+        <v>-17.73530409492577</v>
       </c>
       <c r="F6">
-        <v>-3.493330687513179</v>
+        <v>-4.20271636677898</v>
       </c>
       <c r="G6">
-        <v>-9.212630314444203</v>
+        <v>-10.34746215148759</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.86524150161121</v>
       </c>
       <c r="E7">
-        <v>-15.69031768864596</v>
+        <v>-17.38332845267959</v>
       </c>
       <c r="F7">
-        <v>-3.012421991817925</v>
+        <v>-4.191533406841186</v>
       </c>
       <c r="G7">
-        <v>-9.612484625768456</v>
+        <v>-10.77292353255811</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.94743049620694</v>
       </c>
       <c r="E8">
-        <v>-16.61911223609316</v>
+        <v>-17.31837654998757</v>
       </c>
       <c r="F8">
-        <v>-3.685563283741637</v>
+        <v>-4.059914110210373</v>
       </c>
       <c r="G8">
-        <v>-10.72988644054758</v>
+        <v>-10.54295979721817</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.95143555633692</v>
       </c>
       <c r="E9">
-        <v>-17.48740637079788</v>
+        <v>-18.7783022283724</v>
       </c>
       <c r="F9">
-        <v>-2.756745564576455</v>
+        <v>-3.454686519805179</v>
       </c>
       <c r="G9">
-        <v>-8.525864263413474</v>
+        <v>-10.14337032953706</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.84855956789945</v>
       </c>
       <c r="E10">
-        <v>-19.50905302204215</v>
+        <v>-18.38213773675938</v>
       </c>
       <c r="F10">
-        <v>-3.582304801880471</v>
+        <v>-3.555565930485505</v>
       </c>
       <c r="G10">
-        <v>-8.704090793065678</v>
+        <v>-10.38316638512863</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.63147065796167</v>
       </c>
       <c r="E11">
-        <v>-18.73922149768621</v>
+        <v>-19.76700395846707</v>
       </c>
       <c r="F11">
-        <v>-2.970645766959941</v>
+        <v>-3.425260424555532</v>
       </c>
       <c r="G11">
-        <v>-9.383427979906283</v>
+        <v>-11.08692546641244</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.28536451481186</v>
       </c>
       <c r="E12">
-        <v>-17.76648263846858</v>
+        <v>-19.3741180820356</v>
       </c>
       <c r="F12">
-        <v>-3.149094329605816</v>
+        <v>-3.444341867679019</v>
       </c>
       <c r="G12">
-        <v>-9.344595280730632</v>
+        <v>-10.22538247418143</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.79962462326218</v>
       </c>
       <c r="E13">
-        <v>-19.08493878885379</v>
+        <v>-20.37493348010079</v>
       </c>
       <c r="F13">
-        <v>-2.995794172941531</v>
+        <v>-3.066026474820484</v>
       </c>
       <c r="G13">
-        <v>-8.961760484023772</v>
+        <v>-10.37929304684768</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.20449821832689</v>
       </c>
       <c r="E14">
-        <v>-20.09577117142394</v>
+        <v>-20.58051714310101</v>
       </c>
       <c r="F14">
-        <v>-2.544299146984883</v>
+        <v>-3.353349850318507</v>
       </c>
       <c r="G14">
-        <v>-8.67928156479438</v>
+        <v>-9.095102637254538</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.52182969648407</v>
       </c>
       <c r="E15">
-        <v>-19.41664498144163</v>
+        <v>-21.24035203381064</v>
       </c>
       <c r="F15">
-        <v>-2.433973862810434</v>
+        <v>-2.86993368649498</v>
       </c>
       <c r="G15">
-        <v>-8.312923353236473</v>
+        <v>-9.170576454458843</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.77104012057762</v>
       </c>
       <c r="E16">
-        <v>-19.92018412025053</v>
+        <v>-21.53187707652842</v>
       </c>
       <c r="F16">
-        <v>-2.251366895802505</v>
+        <v>-2.55384690966955</v>
       </c>
       <c r="G16">
-        <v>-7.244726176807536</v>
+        <v>-8.529101976950882</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.00661046240141</v>
       </c>
       <c r="E17">
-        <v>-21.69204920217973</v>
+        <v>-23.60478605353953</v>
       </c>
       <c r="F17">
-        <v>-1.280385275834828</v>
+        <v>-2.57432001002974</v>
       </c>
       <c r="G17">
-        <v>-6.634125846998819</v>
+        <v>-8.803688555614652</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.27413576117254</v>
       </c>
       <c r="E18">
-        <v>-24.99176707260881</v>
+        <v>-23.68748957434162</v>
       </c>
       <c r="F18">
-        <v>-1.63034399576073</v>
+        <v>-2.364066280953378</v>
       </c>
       <c r="G18">
-        <v>-8.244017658382083</v>
+        <v>-8.582037600123828</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.60036097254046</v>
       </c>
       <c r="E19">
-        <v>-25.14170937547678</v>
+        <v>-23.81736168040759</v>
       </c>
       <c r="F19">
-        <v>-1.523796066943046</v>
+        <v>-2.168132539169211</v>
       </c>
       <c r="G19">
-        <v>-6.910056507151533</v>
+        <v>-8.620350543649813</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.02898641594836</v>
       </c>
       <c r="E20">
-        <v>-22.87281257188771</v>
+        <v>-24.57661921795563</v>
       </c>
       <c r="F20">
-        <v>-1.778664007599384</v>
+        <v>-1.760935288444669</v>
       </c>
       <c r="G20">
-        <v>-6.794445635829105</v>
+        <v>-8.833162342550784</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.593345341178097</v>
       </c>
       <c r="E21">
-        <v>-26.10588489034591</v>
+        <v>-26.01752077703424</v>
       </c>
       <c r="F21">
-        <v>-1.399959282061534</v>
+        <v>-1.539062878176641</v>
       </c>
       <c r="G21">
-        <v>-6.94549920769497</v>
+        <v>-8.203648866076209</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.297834877798786</v>
       </c>
       <c r="E22">
-        <v>-25.07163124020808</v>
+        <v>-26.41219540069874</v>
       </c>
       <c r="F22">
-        <v>-1.289465839304316</v>
+        <v>-1.297886193953773</v>
       </c>
       <c r="G22">
-        <v>-6.935246448159847</v>
+        <v>-7.694271776676248</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.142284676965366</v>
       </c>
       <c r="E23">
-        <v>-26.55546726135341</v>
+        <v>-26.68773493016945</v>
       </c>
       <c r="F23">
-        <v>-0.9263211670606522</v>
+        <v>-1.147786848933906</v>
       </c>
       <c r="G23">
-        <v>-6.842279708326034</v>
+        <v>-8.769927612205164</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.130421010347934</v>
       </c>
       <c r="E24">
-        <v>-27.02837580197443</v>
+        <v>-27.7344011275623</v>
       </c>
       <c r="F24">
-        <v>-0.2380373190137653</v>
+        <v>-0.9767720553607532</v>
       </c>
       <c r="G24">
-        <v>-6.104945074182937</v>
+        <v>-7.911864003335926</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.237985983043131</v>
       </c>
       <c r="E25">
-        <v>-27.93427891331286</v>
+        <v>-27.31110654816932</v>
       </c>
       <c r="F25">
-        <v>-0.8271945818046492</v>
+        <v>-0.8552588410440937</v>
       </c>
       <c r="G25">
-        <v>-6.56489571868158</v>
+        <v>-8.785656014062242</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.426429025985888</v>
       </c>
       <c r="E26">
-        <v>-27.06231671466192</v>
+        <v>-27.85764354768105</v>
       </c>
       <c r="F26">
-        <v>-0.1838330980115796</v>
+        <v>-0.7338972179621466</v>
       </c>
       <c r="G26">
-        <v>-6.936166779819764</v>
+        <v>-7.843064245938792</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.679685569444619</v>
       </c>
       <c r="E27">
-        <v>-27.27456176292742</v>
+        <v>-28.86637924678565</v>
       </c>
       <c r="F27">
-        <v>-0.2002637654461078</v>
+        <v>-0.8601155591267072</v>
       </c>
       <c r="G27">
-        <v>-7.015255712752953</v>
+        <v>-7.503193709240595</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.962817362885442</v>
       </c>
       <c r="E28">
-        <v>-27.41500785580131</v>
+        <v>-28.36006868188406</v>
       </c>
       <c r="F28">
-        <v>-0.1849762450274429</v>
+        <v>-1.130122742436609</v>
       </c>
       <c r="G28">
-        <v>-6.613216441372781</v>
+        <v>-8.464824424760392</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.23174333001946</v>
       </c>
       <c r="E29">
-        <v>-28.7511069409204</v>
+        <v>-27.94945835818656</v>
       </c>
       <c r="F29">
-        <v>-0.6831969910738028</v>
+        <v>-0.8440535151864248</v>
       </c>
       <c r="G29">
-        <v>-6.753706062422833</v>
+        <v>-7.826974994617935</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.47338493918347</v>
       </c>
       <c r="E30">
-        <v>-27.82313204726859</v>
+        <v>-28.59646408203247</v>
       </c>
       <c r="F30">
-        <v>-0.2885776709933687</v>
+        <v>-0.9447755360602195</v>
       </c>
       <c r="G30">
-        <v>-6.105670083656038</v>
+        <v>-8.12134539342439</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.67317974121607</v>
       </c>
       <c r="E31">
-        <v>-27.68548907980545</v>
+        <v>-29.04725555560002</v>
       </c>
       <c r="F31">
-        <v>-0.8176211397304953</v>
+        <v>-0.7045812955770721</v>
       </c>
       <c r="G31">
-        <v>-6.40432432839031</v>
+        <v>-8.188830864242432</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.81074074215693</v>
       </c>
       <c r="E32">
-        <v>-27.32710111836441</v>
+        <v>-28.89015826379993</v>
       </c>
       <c r="F32">
-        <v>-0.2287090736908401</v>
+        <v>-0.8930638725730575</v>
       </c>
       <c r="G32">
-        <v>-6.52542077367131</v>
+        <v>-7.956804659031532</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.89313330045151</v>
       </c>
       <c r="E33">
-        <v>-28.28852784951088</v>
+        <v>-28.81158471129284</v>
       </c>
       <c r="F33">
-        <v>-0.6226292516833114</v>
+        <v>-0.9301697620140587</v>
       </c>
       <c r="G33">
-        <v>-6.565206909962271</v>
+        <v>-7.32592723779478</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.93482704720291</v>
       </c>
       <c r="E34">
-        <v>-26.07693888448888</v>
+        <v>-27.63914014833695</v>
       </c>
       <c r="F34">
-        <v>-0.346126011200656</v>
+        <v>-0.9489364255244814</v>
       </c>
       <c r="G34">
-        <v>-5.989546077775022</v>
+        <v>-7.912493006988387</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.94148040960579</v>
       </c>
       <c r="E35">
-        <v>-27.31878684008633</v>
+        <v>-27.72869072183863</v>
       </c>
       <c r="F35">
-        <v>-0.4370741250888193</v>
+        <v>-1.042614010004869</v>
       </c>
       <c r="G35">
-        <v>-7.056018459978</v>
+        <v>-8.284538735782762</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.92567246908766</v>
       </c>
       <c r="E36">
-        <v>-25.78995137272678</v>
+        <v>-27.79825261107045</v>
       </c>
       <c r="F36">
-        <v>-0.6882765399877694</v>
+        <v>-1.174591989721095</v>
       </c>
       <c r="G36">
-        <v>-6.778611296514771</v>
+        <v>-7.693483866837902</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.91188684062037</v>
       </c>
       <c r="E37">
-        <v>-26.55025951624459</v>
+        <v>-27.48106923462521</v>
       </c>
       <c r="F37">
-        <v>-0.9439488253922256</v>
+        <v>-1.313267319888954</v>
       </c>
       <c r="G37">
-        <v>-7.018553016110068</v>
+        <v>-7.548786542407437</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.90833876382064</v>
       </c>
       <c r="E38">
-        <v>-24.81414220813195</v>
+        <v>-26.80763080799653</v>
       </c>
       <c r="F38">
-        <v>-0.5777350519211893</v>
+        <v>-1.34453653260983</v>
       </c>
       <c r="G38">
-        <v>-6.586159352680318</v>
+        <v>-7.6557006105982</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.91274543050114</v>
       </c>
       <c r="E39">
-        <v>-24.74017864216467</v>
+        <v>-26.21886125988927</v>
       </c>
       <c r="F39">
-        <v>-0.3754982625691208</v>
+        <v>-1.227036758359734</v>
       </c>
       <c r="G39">
-        <v>-6.557387401398513</v>
+        <v>-7.167411696283397</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.9431713594504</v>
       </c>
       <c r="E40">
-        <v>-24.77092698067675</v>
+        <v>-25.89177411078925</v>
       </c>
       <c r="F40">
-        <v>-0.7850431065131964</v>
+        <v>-1.223457382812237</v>
       </c>
       <c r="G40">
-        <v>-5.551971410576313</v>
+        <v>-7.420622082400093</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.99945241012557</v>
       </c>
       <c r="E41">
-        <v>-23.14812567765804</v>
+        <v>-26.09373499458333</v>
       </c>
       <c r="F41">
-        <v>-1.019307893127105</v>
+        <v>-1.267144651268481</v>
       </c>
       <c r="G41">
-        <v>-5.656187384152571</v>
+        <v>-7.046550299735684</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.0645416475954</v>
       </c>
       <c r="E42">
-        <v>-23.94534541281237</v>
+        <v>-25.74992871944699</v>
       </c>
       <c r="F42">
-        <v>-0.7273763097673088</v>
+        <v>-1.451887149440827</v>
       </c>
       <c r="G42">
-        <v>-6.14277467806019</v>
+        <v>-7.495576143954731</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.14436599784434</v>
       </c>
       <c r="E43">
-        <v>-23.84027575888641</v>
+        <v>-26.72895310058727</v>
       </c>
       <c r="F43">
-        <v>-0.7015428439436034</v>
+        <v>-0.9980561274082836</v>
       </c>
       <c r="G43">
-        <v>-5.790267789038593</v>
+        <v>-6.873617332400775</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.23496055769436</v>
       </c>
       <c r="E44">
-        <v>-23.3103990152489</v>
+        <v>-23.56613099941006</v>
       </c>
       <c r="F44">
-        <v>-0.867846712097035</v>
+        <v>-1.515996159478286</v>
       </c>
       <c r="G44">
-        <v>-6.187622638480696</v>
+        <v>-7.305600488183654</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.31653478734996</v>
       </c>
       <c r="E45">
-        <v>-22.25572647581049</v>
+        <v>-24.44572820523792</v>
       </c>
       <c r="F45">
-        <v>-0.5714427731295243</v>
+        <v>-1.352301648643673</v>
       </c>
       <c r="G45">
-        <v>-5.840412622321934</v>
+        <v>-7.094331403503985</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.38746603414511</v>
       </c>
       <c r="E46">
-        <v>-22.35000477617617</v>
+        <v>-23.73576763573739</v>
       </c>
       <c r="F46">
-        <v>-0.5385963488737183</v>
+        <v>-1.138043591542178</v>
       </c>
       <c r="G46">
-        <v>-6.092057120398555</v>
+        <v>-6.369666227139679</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.44884847713685</v>
       </c>
       <c r="E47">
-        <v>-22.89054154762774</v>
+        <v>-22.94833846138764</v>
       </c>
       <c r="F47">
-        <v>-0.7876996807739745</v>
+        <v>-0.7831975039397592</v>
       </c>
       <c r="G47">
-        <v>-5.608134815650049</v>
+        <v>-6.764740110705224</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.48868944873624</v>
       </c>
       <c r="E48">
-        <v>-21.15352307318757</v>
+        <v>-22.82916713940178</v>
       </c>
       <c r="F48">
-        <v>-0.437616705737653</v>
+        <v>-1.464313488850222</v>
       </c>
       <c r="G48">
-        <v>-5.212362406975719</v>
+        <v>-7.141298113069626</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.50013635428937</v>
       </c>
       <c r="E49">
-        <v>-19.97533187671594</v>
+        <v>-22.77674552428899</v>
       </c>
       <c r="F49">
-        <v>-0.7577682814086198</v>
+        <v>-1.364265759042306</v>
       </c>
       <c r="G49">
-        <v>-6.080480142647724</v>
+        <v>-6.85051634562774</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.493459506047</v>
       </c>
       <c r="E50">
-        <v>-20.4699318078337</v>
+        <v>-21.91187038746006</v>
       </c>
       <c r="F50">
-        <v>-1.441124171776252</v>
+        <v>-1.297474495354582</v>
       </c>
       <c r="G50">
-        <v>-6.02194307642233</v>
+        <v>-7.122444556223476</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.46539339186103</v>
       </c>
       <c r="E51">
-        <v>-19.80292381429591</v>
+        <v>-21.30938862005757</v>
       </c>
       <c r="F51">
-        <v>-0.7775753743769589</v>
+        <v>-1.553439194452226</v>
       </c>
       <c r="G51">
-        <v>-4.4563198799902</v>
+        <v>-6.41917212513394</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.40638486751176</v>
       </c>
       <c r="E52">
-        <v>-19.33850616243928</v>
+        <v>-21.45443564252325</v>
       </c>
       <c r="F52">
-        <v>-0.8670481659207363</v>
+        <v>-1.64411808893448</v>
       </c>
       <c r="G52">
-        <v>-5.929251111868276</v>
+        <v>-6.759469722206704</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.33190969118237</v>
       </c>
       <c r="E53">
-        <v>-19.25131039542159</v>
+        <v>-20.41670865282155</v>
       </c>
       <c r="F53">
-        <v>-0.7160019969594689</v>
+        <v>-1.274640547896413</v>
       </c>
       <c r="G53">
-        <v>-5.637267616395636</v>
+        <v>-7.195319595179453</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.24429764553139</v>
       </c>
       <c r="E54">
-        <v>-19.13253757914841</v>
+        <v>-19.90266345431485</v>
       </c>
       <c r="F54">
-        <v>-1.155113758611667</v>
+        <v>-1.33330718409748</v>
       </c>
       <c r="G54">
-        <v>-6.576936172807909</v>
+        <v>-7.949640638484549</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.13338785907298</v>
       </c>
       <c r="E55">
-        <v>-19.01045444837563</v>
+        <v>-20.24336772475594</v>
       </c>
       <c r="F55">
-        <v>-0.5388755086884618</v>
+        <v>-1.373760506213194</v>
       </c>
       <c r="G55">
-        <v>-6.558115721417153</v>
+        <v>-7.52829095497381</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.01296726082704</v>
       </c>
       <c r="E56">
-        <v>-17.82490448164153</v>
+        <v>-19.18831479350089</v>
       </c>
       <c r="F56">
-        <v>-1.618504968839919</v>
+        <v>-1.13022960183157</v>
       </c>
       <c r="G56">
-        <v>-5.096165569092839</v>
+        <v>-7.159681572449198</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.88941135066864</v>
       </c>
       <c r="E57">
-        <v>-17.11032939712718</v>
+        <v>-19.39474528114054</v>
       </c>
       <c r="F57">
-        <v>-1.086764335839277</v>
+        <v>-1.502383597948082</v>
       </c>
       <c r="G57">
-        <v>-6.432765225118188</v>
+        <v>-7.85969973727363</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.75486224673439</v>
       </c>
       <c r="E58">
-        <v>-18.28555897159779</v>
+        <v>-18.48713040662722</v>
       </c>
       <c r="F58">
-        <v>-0.04608968117186944</v>
+        <v>-1.376393057819291</v>
       </c>
       <c r="G58">
-        <v>-6.250496519362534</v>
+        <v>-7.673782810333699</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.61550873415176</v>
       </c>
       <c r="E59">
-        <v>-17.1606407433524</v>
+        <v>-18.92869737864114</v>
       </c>
       <c r="F59">
-        <v>-1.217522130371179</v>
+        <v>-1.020364889933077</v>
       </c>
       <c r="G59">
-        <v>-6.083611918727874</v>
+        <v>-7.624700662168465</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.48054952400326</v>
       </c>
       <c r="E60">
-        <v>-14.98882536553976</v>
+        <v>-18.32113919187606</v>
       </c>
       <c r="F60">
-        <v>-0.8394038889545112</v>
+        <v>-1.477839900170535</v>
       </c>
       <c r="G60">
-        <v>-6.183484456556607</v>
+        <v>-7.221135229294689</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.34425222318612</v>
       </c>
       <c r="E61">
-        <v>-15.15243460296289</v>
+        <v>-17.49229259425215</v>
       </c>
       <c r="F61">
-        <v>-0.5878386491331349</v>
+        <v>-1.472301435715417</v>
       </c>
       <c r="G61">
-        <v>-6.575439806224158</v>
+        <v>-7.810842706205066</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.2011616276171</v>
       </c>
       <c r="E62">
-        <v>-15.61301663733502</v>
+        <v>-17.41505947005134</v>
       </c>
       <c r="F62">
-        <v>-0.6397706583494416</v>
+        <v>-1.811186540200695</v>
       </c>
       <c r="G62">
-        <v>-7.088690233905067</v>
+        <v>-7.362128053266709</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.06149766731206</v>
       </c>
       <c r="E63">
-        <v>-15.52183581319058</v>
+        <v>-18.06307504360095</v>
       </c>
       <c r="F63">
-        <v>-1.174832216267907</v>
+        <v>-1.463896820046614</v>
       </c>
       <c r="G63">
-        <v>-6.718468615702831</v>
+        <v>-8.09431478909624</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.92074541335359</v>
       </c>
       <c r="E64">
-        <v>-15.46279809755258</v>
+        <v>-16.8041049277805</v>
       </c>
       <c r="F64">
-        <v>-1.163822385117298</v>
+        <v>-1.338092662583453</v>
       </c>
       <c r="G64">
-        <v>-6.709695670023762</v>
+        <v>-7.846894547127729</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.766936156559597</v>
       </c>
       <c r="E65">
-        <v>-15.70249928372659</v>
+        <v>-16.70818731982403</v>
       </c>
       <c r="F65">
-        <v>-0.5747786086605979</v>
+        <v>-1.932240838976204</v>
       </c>
       <c r="G65">
-        <v>-5.898873545999924</v>
+        <v>-8.188860659152285</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.611167413282317</v>
       </c>
       <c r="E66">
-        <v>-15.25388147768272</v>
+        <v>-16.66019908076475</v>
       </c>
       <c r="F66">
-        <v>-1.195038582324395</v>
+        <v>-1.414890604496995</v>
       </c>
       <c r="G66">
-        <v>-6.900518825452893</v>
+        <v>-7.900002318668717</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.45287360558949</v>
       </c>
       <c r="E67">
-        <v>-14.6430582611581</v>
+        <v>-16.7708070584021</v>
       </c>
       <c r="F67">
-        <v>-0.9208605691413978</v>
+        <v>-1.777654227735371</v>
       </c>
       <c r="G67">
-        <v>-6.869469218840068</v>
+        <v>-8.856786395519022</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.280494811690454</v>
       </c>
       <c r="E68">
-        <v>-15.51625220473912</v>
+        <v>-16.20933515161307</v>
       </c>
       <c r="F68">
-        <v>-1.849745386066207</v>
+        <v>-1.462636044859553</v>
       </c>
       <c r="G68">
-        <v>-6.827448464310099</v>
+        <v>-7.960118515116343</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.102943215756785</v>
       </c>
       <c r="E69">
-        <v>-15.99908263191094</v>
+        <v>-15.80011054096192</v>
       </c>
       <c r="F69">
-        <v>-1.230742045752456</v>
+        <v>-1.646845074424496</v>
       </c>
       <c r="G69">
-        <v>-5.459858791491632</v>
+        <v>-7.955977022646715</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.923567305468042</v>
       </c>
       <c r="E70">
-        <v>-14.33502693068236</v>
+        <v>-15.24327579155675</v>
       </c>
       <c r="F70">
-        <v>-1.359021365015182</v>
+        <v>-1.256795857305306</v>
       </c>
       <c r="G70">
-        <v>-6.572245129778762</v>
+        <v>-8.697777582722289</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.734807163356368</v>
       </c>
       <c r="E71">
-        <v>-14.12041349051084</v>
+        <v>-16.99304192032852</v>
       </c>
       <c r="F71">
-        <v>-0.6295494329662984</v>
+        <v>-1.971152569355308</v>
       </c>
       <c r="G71">
-        <v>-6.696979864607421</v>
+        <v>-8.518243387582073</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.540851351969943</v>
       </c>
       <c r="E72">
-        <v>-13.37998081941269</v>
+        <v>-16.16115218817146</v>
       </c>
       <c r="F72">
-        <v>-1.218629657588722</v>
+        <v>-1.451786916985088</v>
       </c>
       <c r="G72">
-        <v>-7.015619872762273</v>
+        <v>-8.713307351847009</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.351345542692281</v>
       </c>
       <c r="E73">
-        <v>-15.04325762311196</v>
+        <v>-17.12785912001087</v>
       </c>
       <c r="F73">
-        <v>-1.054025599345835</v>
+        <v>-1.712659692944319</v>
       </c>
       <c r="G73">
-        <v>-6.523023938700877</v>
+        <v>-8.084730759760049</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.164907211507614</v>
       </c>
       <c r="E74">
-        <v>-15.94136723068319</v>
+        <v>-16.10397114687661</v>
       </c>
       <c r="F74">
-        <v>-1.32942214097835</v>
+        <v>-1.839186186782721</v>
       </c>
       <c r="G74">
-        <v>-7.16121766557942</v>
+        <v>-8.071220423414283</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.979571629587065</v>
       </c>
       <c r="E75">
-        <v>-17.31725801690768</v>
+        <v>-16.38514862648687</v>
       </c>
       <c r="F75">
-        <v>-1.127172097747837</v>
+        <v>-1.900523479490414</v>
       </c>
       <c r="G75">
-        <v>-6.649486778301037</v>
+        <v>-8.102849375496481</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.808029507627755</v>
       </c>
       <c r="E76">
-        <v>-15.8460292673997</v>
+        <v>-17.31741651349795</v>
       </c>
       <c r="F76">
-        <v>-1.21056881439208</v>
+        <v>-2.214595666792235</v>
       </c>
       <c r="G76">
-        <v>-6.858885404751018</v>
+        <v>-8.269174493935004</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.649677244040069</v>
       </c>
       <c r="E77">
-        <v>-15.35448152776311</v>
+        <v>-18.05600609567497</v>
       </c>
       <c r="F77">
-        <v>-1.534642709715303</v>
+        <v>-2.317306597800151</v>
       </c>
       <c r="G77">
-        <v>-5.627908704156116</v>
+        <v>-7.874732924567461</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.496484659459995</v>
       </c>
       <c r="E78">
-        <v>-16.3641500925133</v>
+        <v>-18.17486042448029</v>
       </c>
       <c r="F78">
-        <v>-2.34380689938311</v>
+        <v>-2.194198776233103</v>
       </c>
       <c r="G78">
-        <v>-6.560433103294642</v>
+        <v>-8.11175805354266</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.358256805425017</v>
       </c>
       <c r="E79">
-        <v>-15.85963280331874</v>
+        <v>-17.7326096528912</v>
       </c>
       <c r="F79">
-        <v>-1.319229080086902</v>
+        <v>-2.091332940520863</v>
       </c>
       <c r="G79">
-        <v>-6.523997239089423</v>
+        <v>-8.371735194741627</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.234674372534418</v>
       </c>
       <c r="E80">
-        <v>-16.28985594794346</v>
+        <v>-17.78797024763497</v>
       </c>
       <c r="F80">
-        <v>-1.83939576373563</v>
+        <v>-2.275719240710005</v>
       </c>
       <c r="G80">
-        <v>-6.071064951134036</v>
+        <v>-7.380395643552408</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.114466741567541</v>
       </c>
       <c r="E81">
-        <v>-16.73619593156147</v>
+        <v>-19.00534180122096</v>
       </c>
       <c r="F81">
-        <v>-2.187182504331391</v>
+        <v>-2.335913386401834</v>
       </c>
       <c r="G81">
-        <v>-6.631417820747695</v>
+        <v>-7.157708487307793</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.002387861764491</v>
       </c>
       <c r="E82">
-        <v>-18.38294833360675</v>
+        <v>-19.81806250290355</v>
       </c>
       <c r="F82">
-        <v>-2.276160760535697</v>
+        <v>-2.369255174364514</v>
       </c>
       <c r="G82">
-        <v>-6.292967508085844</v>
+        <v>-8.252532381509088</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.89882877991301</v>
       </c>
       <c r="E83">
-        <v>-18.98701053843791</v>
+        <v>-20.44430064495028</v>
       </c>
       <c r="F83">
-        <v>-2.649544882245366</v>
+        <v>-2.646957890846423</v>
       </c>
       <c r="G83">
-        <v>-5.52418600186521</v>
+        <v>-6.857534702170995</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.795150272670298</v>
       </c>
       <c r="E84">
-        <v>-19.28948543130625</v>
+        <v>-21.52219067062602</v>
       </c>
       <c r="F84">
-        <v>-1.816991738959514</v>
+        <v>-2.420137642081473</v>
       </c>
       <c r="G84">
-        <v>-5.62216821819102</v>
+        <v>-7.297406887973958</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.69260782496113</v>
       </c>
       <c r="E85">
-        <v>-21.09123844168607</v>
+        <v>-21.99546601764165</v>
       </c>
       <c r="F85">
-        <v>-1.547805467745787</v>
+        <v>-2.573365730781715</v>
       </c>
       <c r="G85">
-        <v>-5.242802873209317</v>
+        <v>-7.844186520876606</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.599997554968865</v>
       </c>
       <c r="E86">
-        <v>-21.86078014370552</v>
+        <v>-23.13293717583631</v>
       </c>
       <c r="F86">
-        <v>-2.614645763565422</v>
+        <v>-3.04179424318639</v>
       </c>
       <c r="G86">
-        <v>-6.927224996318193</v>
+        <v>-7.942996373587232</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.51811251510059</v>
       </c>
       <c r="E87">
-        <v>-21.85140620250965</v>
+        <v>-24.165927381726</v>
       </c>
       <c r="F87">
-        <v>-2.533314166856359</v>
+        <v>-2.752348590402395</v>
       </c>
       <c r="G87">
-        <v>-6.38647055629702</v>
+        <v>-7.590714601662307</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.448546193221269</v>
       </c>
       <c r="E88">
-        <v>-23.42654984507163</v>
+        <v>-24.04381708010916</v>
       </c>
       <c r="F88">
-        <v>-2.405317320877987</v>
+        <v>-3.309044619779775</v>
       </c>
       <c r="G88">
-        <v>-4.643584198964614</v>
+        <v>-7.887346103072083</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.409255706231842</v>
       </c>
       <c r="E89">
-        <v>-24.74340744413213</v>
+        <v>-26.4428712836267</v>
       </c>
       <c r="F89">
-        <v>-2.557853722796891</v>
+        <v>-3.265028489464621</v>
       </c>
       <c r="G89">
-        <v>-5.274272919105629</v>
+        <v>-7.956970186308496</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.408291120391439</v>
       </c>
       <c r="E90">
-        <v>-26.22133833517146</v>
+        <v>-27.56677513369437</v>
       </c>
       <c r="F90">
-        <v>-3.05276017086465</v>
+        <v>-3.312445067968267</v>
       </c>
       <c r="G90">
-        <v>-7.366954828662967</v>
+        <v>-7.966388688367722</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.44599397556194</v>
       </c>
       <c r="E91">
-        <v>-29.24486910434674</v>
+        <v>-28.19721569962022</v>
       </c>
       <c r="F91">
-        <v>-3.246615538835193</v>
+        <v>-3.129627695640028</v>
       </c>
       <c r="G91">
-        <v>-7.135603974742079</v>
+        <v>-7.996024692035278</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.541181922331527</v>
       </c>
       <c r="E92">
-        <v>-28.92152700325106</v>
+        <v>-29.9255576178617</v>
       </c>
       <c r="F92">
-        <v>-3.425942999295439</v>
+        <v>-3.67306239126599</v>
       </c>
       <c r="G92">
-        <v>-8.656428868936791</v>
+        <v>-8.709821347394156</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.703054415323304</v>
       </c>
       <c r="E93">
-        <v>-30.50696386723248</v>
+        <v>-31.99579932368228</v>
       </c>
       <c r="F93">
-        <v>-3.084991118140176</v>
+        <v>-3.34273680715384</v>
       </c>
       <c r="G93">
-        <v>-7.38220320141685</v>
+        <v>-8.093394457436322</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.924933866676214</v>
       </c>
       <c r="E94">
-        <v>-33.37817488468576</v>
+        <v>-33.57526313044759</v>
       </c>
       <c r="F94">
-        <v>-3.151080754637729</v>
+        <v>-3.52398607998858</v>
       </c>
       <c r="G94">
-        <v>-7.068274099564381</v>
+        <v>-8.558026213327494</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.215113108752585</v>
       </c>
       <c r="E95">
-        <v>-34.24072012163774</v>
+        <v>-35.05606507400778</v>
       </c>
       <c r="F95">
-        <v>-2.833438303829842</v>
+        <v>-3.628959282373541</v>
       </c>
       <c r="G95">
-        <v>-7.45070500971545</v>
+        <v>-8.304372214108536</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.57718255879545</v>
       </c>
       <c r="E96">
-        <v>-35.72401951861316</v>
+        <v>-37.53792695322957</v>
       </c>
       <c r="F96">
-        <v>-3.653818588131555</v>
+        <v>-3.627423489208751</v>
       </c>
       <c r="G96">
-        <v>-6.940334756653707</v>
+        <v>-9.455604493753473</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.989979588982218</v>
       </c>
       <c r="E97">
-        <v>-37.15669510465684</v>
+        <v>-38.38487386146214</v>
       </c>
       <c r="F97">
-        <v>-3.335298896244103</v>
+        <v>-3.560709263689487</v>
       </c>
       <c r="G97">
-        <v>-7.890371941694977</v>
+        <v>-8.873862189410584</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.452349182199853</v>
       </c>
       <c r="E98">
-        <v>-40.76364955837332</v>
+        <v>-40.78344125402384</v>
       </c>
       <c r="F98">
-        <v>-3.562607053409301</v>
+        <v>-3.602938605516803</v>
       </c>
       <c r="G98">
-        <v>-6.994045047482843</v>
+        <v>-9.369030417355992</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.940300770367358</v>
       </c>
       <c r="E99">
-        <v>-43.00840959550151</v>
+        <v>-43.38870178571765</v>
       </c>
       <c r="F99">
-        <v>-4.000303963537518</v>
+        <v>-3.822948017495935</v>
       </c>
       <c r="G99">
-        <v>-8.216202454761126</v>
+        <v>-10.01405711022759</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.457184500842107</v>
       </c>
       <c r="E100">
-        <v>-43.89753244640451</v>
+        <v>-44.79606546629545</v>
       </c>
       <c r="F100">
-        <v>-3.527240735514179</v>
+        <v>-3.988577594583488</v>
       </c>
       <c r="G100">
-        <v>-7.97739294174026</v>
+        <v>-9.531783457157642</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.940073465125042</v>
       </c>
       <c r="E101">
-        <v>-47.00876843592334</v>
+        <v>-46.84144584981393</v>
       </c>
       <c r="F101">
-        <v>-3.417117572986013</v>
+        <v>-3.794036338403427</v>
       </c>
       <c r="G101">
-        <v>-7.969139751710856</v>
+        <v>-10.27679855695185</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.4482700640741</v>
       </c>
       <c r="E102">
-        <v>-48.66000176299922</v>
+        <v>-49.2110015736455</v>
       </c>
       <c r="F102">
-        <v>-3.483801977278776</v>
+        <v>-4.025970099145858</v>
       </c>
       <c r="G102">
-        <v>-8.015245719436287</v>
+        <v>-9.6456264971621</v>
       </c>
     </row>
   </sheetData>
